--- a/reports/portfolio_260528.xlsx
+++ b/reports/portfolio_260528.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taeoh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taeoh\SynologyDrive_ludwizia\MyInvestments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBEA663-43B2-4FD6-A067-A8735F5A8815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464B97D3-F92F-40BF-A846-1262489234CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14640" yWindow="1700" windowWidth="21480" windowHeight="16950" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38490" yWindow="2280" windowWidth="22640" windowHeight="18770" tabRatio="661" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assets" sheetId="1" r:id="rId1"/>
@@ -83,6 +83,9 @@
     <t>원금</t>
   </si>
   <si>
+    <t>차익</t>
+  </si>
+  <si>
     <t>배당수익</t>
   </si>
   <si>
@@ -209,18 +212,14 @@
     <t>481060</t>
   </si>
   <si>
-    <t>KODEX 미국30년국채타겟커버드콜</t>
-  </si>
-  <si>
-    <t>487240</t>
+    <t>TIGER 단기채권액티브</t>
+  </si>
+  <si>
+    <t>278530</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>KODEX AI전력핵심설비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>차익</t>
+    <t>KODEX 200TR</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -228,11 +227,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -304,6 +304,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -331,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -416,15 +423,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -444,7 +442,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -541,6 +539,9 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -554,9 +555,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -594,16 +592,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="2">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,18 +1153,18 @@
       </c>
       <c r="C5" s="24">
         <f>G5-I5</f>
-        <v>1194771396</v>
+        <v>1190574516</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="24">
         <f>C5*(1-D5)</f>
-        <v>1194771396</v>
+        <v>1190574516</v>
       </c>
       <c r="F5" s="24">
         <f>CMA!I10</f>
-        <v>270215212</v>
+        <v>289287262</v>
       </c>
       <c r="G5" s="25">
         <v>1285263124</v>
@@ -1180,7 +1172,7 @@
       <c r="H5" s="25"/>
       <c r="I5" s="26">
         <f>CMA!I14</f>
-        <v>90491728</v>
+        <v>94688608</v>
       </c>
       <c r="K5" s="18">
         <v>0.4</v>
@@ -1192,28 +1184,28 @@
       </c>
       <c r="C6" s="24">
         <f>G6-I6</f>
-        <v>123930727</v>
+        <v>126027752</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="24">
         <f>C6*(1-D6)</f>
-        <v>123930727</v>
+        <v>126027752</v>
       </c>
       <c r="F6" s="24">
         <f>개인연금!F10</f>
-        <v>98536896</v>
+        <v>87721508</v>
       </c>
       <c r="G6" s="25">
-        <v>133772341</v>
+        <v>135409684</v>
       </c>
       <c r="H6" s="25">
         <v>0</v>
       </c>
       <c r="I6" s="26">
         <f>개인연금!F14+H6</f>
-        <v>9841614</v>
+        <v>9381932</v>
       </c>
       <c r="K6" s="18">
         <v>0.3</v>
@@ -1225,28 +1217,28 @@
       </c>
       <c r="C7" s="24">
         <f>G7-I7</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="24">
         <f>C7*(1-D7)</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
       <c r="F7" s="24">
         <f>퇴직연금!F10</f>
         <v>13613677</v>
       </c>
       <c r="G7" s="25">
-        <v>13756508</v>
+        <v>13831510</v>
       </c>
       <c r="H7" s="25">
         <v>0</v>
       </c>
       <c r="I7" s="26">
         <f>퇴직연금!F14+H7</f>
-        <v>102718</v>
+        <v>208978</v>
       </c>
       <c r="K7" s="18">
         <v>0.2</v>
@@ -1268,11 +1260,11 @@
       <c r="A10" s="21"/>
       <c r="B10" s="20">
         <f>C19/C13</f>
-        <v>7.5382305148369161E-2</v>
+        <v>7.8392402547298776E-2</v>
       </c>
       <c r="C10" s="28">
         <f>SUM(G5,G6,G7)</f>
-        <v>1432791973</v>
+        <v>1434504318</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1286,7 +1278,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="28">
         <f>SUM(C5,C6,C7)</f>
-        <v>1332355913</v>
+        <v>1330224800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -1301,34 +1293,34 @@
     <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="20">
         <f>C16/C13</f>
-        <v>0.28698471727351427</v>
+        <v>0.29365145425043948</v>
       </c>
       <c r="C16" s="29">
         <f>SUM(F5:F7)</f>
-        <v>382365785</v>
+        <v>390622447</v>
       </c>
     </row>
     <row r="17" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45"/>
     <row r="18" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="48" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C18" s="49"/>
     </row>
     <row r="19" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="20">
         <f>C19/C16</f>
-        <v>0.26267010266098995</v>
+        <v>0.26695731082755725</v>
       </c>
       <c r="C19" s="28">
         <f>SUM(I5,I6,I7)</f>
-        <v>100436060</v>
+        <v>104279518</v>
       </c>
     </row>
     <row r="20" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -1343,7 +1335,7 @@
       </c>
       <c r="D22" s="20">
         <f>C22/C16</f>
-        <v>1.11461358918398E-2</v>
+        <v>1.0910537867784132E-2</v>
       </c>
     </row>
     <row r="23" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.45"/>
@@ -1380,16 +1372,16 @@
     <row r="1" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="5">
         <v>3</v>
@@ -1401,25 +1393,25 @@
         <v>5</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B3" s="52"/>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="52"/>
@@ -1427,29 +1419,29 @@
     <row r="4" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="53"/>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="53"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" s="55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="30">
         <v>0.4</v>
@@ -1472,7 +1464,7 @@
     <row r="6" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="52"/>
       <c r="C6" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="30">
         <v>0.4</v>
@@ -1484,7 +1476,7 @@
         <v>0.1</v>
       </c>
       <c r="G6" s="30">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" s="30"/>
       <c r="I6" s="18"/>
@@ -1492,23 +1484,23 @@
     <row r="7" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="53"/>
       <c r="C7" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="31">
         <f>Assets!$E$5*(D5)*D6</f>
-        <v>191163423.36000001</v>
+        <v>190491922.56000003</v>
       </c>
       <c r="E7" s="31">
         <f>Assets!$E$5*(E5)*E6</f>
-        <v>143372567.52000001</v>
+        <v>142868941.92000002</v>
       </c>
       <c r="F7" s="31">
         <f>Assets!$E$5*(F5)*F6</f>
-        <v>23895427.920000002</v>
+        <v>23811490.320000004</v>
       </c>
       <c r="G7" s="31">
         <f>Assets!$E$5*(G5)*G6</f>
-        <v>11947713.960000001</v>
+        <v>23811490.320000004</v>
       </c>
       <c r="H7" s="31">
         <f>Assets!$E$5*(H5)*H6</f>
@@ -1516,40 +1508,48 @@
       </c>
       <c r="I7" s="32">
         <f>SUM(D7:G7)</f>
-        <v>370379132.75999999</v>
+        <v>380983845.12</v>
       </c>
     </row>
     <row r="8" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="59">
+        <v>32</v>
+      </c>
+      <c r="D8" s="34">
         <v>8597</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="34">
         <v>874</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
+      <c r="F8" s="34">
+        <v>237</v>
+      </c>
+      <c r="G8" s="34">
+        <v>197</v>
+      </c>
       <c r="H8" s="34"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="52"/>
       <c r="C9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="59">
+        <v>33</v>
+      </c>
+      <c r="D9" s="34">
         <v>19902</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="34">
         <v>113407</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
+      <c r="F9" s="34">
+        <v>40200</v>
+      </c>
+      <c r="G9" s="34">
+        <v>48450</v>
+      </c>
       <c r="H9" s="34"/>
       <c r="I9" s="8"/>
     </row>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="F10" s="31">
         <f>F9*F8</f>
-        <v>0</v>
+        <v>9527400</v>
       </c>
       <c r="G10" s="31">
         <f>G9*G8</f>
-        <v>0</v>
+        <v>9544650</v>
       </c>
       <c r="H10" s="31">
         <f>H9*H8</f>
@@ -1580,29 +1580,29 @@
       </c>
       <c r="I10" s="35">
         <f>SUM(D10:G10)</f>
-        <v>270215212</v>
+        <v>289287262</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="53"/>
       <c r="C11" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="36">
         <f>D10/$I$10</f>
-        <v>0.63318971842340244</v>
+        <v>0.59144496310383687</v>
       </c>
       <c r="E11" s="36">
         <f>E10/$I$10</f>
-        <v>0.36681028157659756</v>
+        <v>0.34262731554353748</v>
       </c>
       <c r="F11" s="36">
         <f>F10/$I$10</f>
-        <v>0</v>
+        <v>3.2934046021010077E-2</v>
       </c>
       <c r="G11" s="36">
         <f>G10/$I$10</f>
-        <v>0</v>
+        <v>3.2993675331615534E-2</v>
       </c>
       <c r="H11" s="36">
         <f>H10/$I$10</f>
@@ -1615,36 +1615,38 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B12" s="56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="60">
-        <v>25620</v>
-      </c>
-      <c r="E12" s="60">
-        <v>160700</v>
+        <v>36</v>
+      </c>
+      <c r="D12" s="38">
+        <v>26250</v>
+      </c>
+      <c r="E12" s="38">
+        <v>159305</v>
       </c>
       <c r="F12" s="38">
-        <v>33770</v>
-      </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
+        <v>40200</v>
+      </c>
+      <c r="G12" s="38">
+        <v>48450</v>
+      </c>
+      <c r="H12" s="39"/>
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B13" s="50"/>
       <c r="C13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="9">
         <f>IF(D9&gt;0, (D12-D9)/D9, 0)</f>
-        <v>0.28730780826047636</v>
+        <v>0.31896291829966839</v>
       </c>
       <c r="E13" s="9">
         <f>IF(E9&gt;0, (E12-E9)/E9, 0)</f>
-        <v>0.41702011339688028</v>
+        <v>0.40471928540566277</v>
       </c>
       <c r="F13" s="9">
         <f>IF(F9&gt;0, (F12-F9)/F9, 0)</f>
@@ -1660,103 +1662,103 @@
       </c>
       <c r="I13" s="9">
         <f>I14/I10</f>
-        <v>0.33488761543151019</v>
+        <v>0.32731689375248052</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B14" s="50"/>
       <c r="C14" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="39">
+        <v>38</v>
+      </c>
+      <c r="D14" s="40">
         <f>D10*D13</f>
-        <v>49157646.000000007</v>
-      </c>
-      <c r="E14" s="39">
+        <v>54573756</v>
+      </c>
+      <c r="E14" s="40">
         <f>E10*E13</f>
-        <v>41334082</v>
-      </c>
-      <c r="F14" s="39">
+        <v>40114852</v>
+      </c>
+      <c r="F14" s="40">
         <f>F10*F13</f>
         <v>0</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="40">
         <f>G10*G13</f>
         <v>0</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="40">
         <f>H10*H13</f>
         <v>0</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="40">
         <f>SUM(D14:G14)</f>
-        <v>90491728</v>
+        <v>94688608</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B15" s="50"/>
       <c r="C15" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="39">
+        <v>35</v>
+      </c>
+      <c r="D15" s="40">
         <f>D7-D10</f>
-        <v>20065929.360000014</v>
-      </c>
-      <c r="E15" s="39">
+        <v>19394428.560000032</v>
+      </c>
+      <c r="E15" s="40">
         <f>E7-E10</f>
-        <v>44254849.520000011</v>
-      </c>
-      <c r="F15" s="39">
+        <v>43751223.920000017</v>
+      </c>
+      <c r="F15" s="40">
         <f>F7-F10</f>
-        <v>23895427.920000002</v>
-      </c>
-      <c r="G15" s="39">
+        <v>14284090.320000004</v>
+      </c>
+      <c r="G15" s="40">
         <f>G7-G10</f>
-        <v>11947713.960000001</v>
-      </c>
-      <c r="H15" s="39">
+        <v>14266840.320000004</v>
+      </c>
+      <c r="H15" s="40">
         <f>H7-H10</f>
         <v>0</v>
       </c>
       <c r="I15" s="24">
         <f>SUM(D15:G15)</f>
-        <v>100163920.76000002</v>
+        <v>91696583.120000064</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="50"/>
       <c r="C16" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="24">
-        <f t="shared" ref="D16:E16" si="0">IFERROR((D7-D10)/D12, 0)</f>
-        <v>783.21348009367739</v>
+        <f t="shared" ref="D16:I16" si="0">IFERROR((D7-D10)/D12, 0)</f>
+        <v>738.8353737142869</v>
       </c>
       <c r="E16" s="24">
         <f t="shared" si="0"/>
-        <v>275.38798705662731</v>
+        <v>274.63810878503512</v>
       </c>
       <c r="F16" s="24">
-        <f t="shared" ref="F16:I16" si="1">IFERROR((F7-F10)/F12, 0)</f>
-        <v>707.5933645247261</v>
+        <f t="shared" ref="F16:G16" si="1">IFERROR((F7-F10)/F12, 0)</f>
+        <v>355.3256298507464</v>
       </c>
       <c r="G16" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>294.46522848297224</v>
       </c>
       <c r="H16" s="24">
-        <f t="shared" ref="H16" si="2">IFERROR((H7-H10)/H12, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="40">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="49"/>
       <c r="C17" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="34">
         <v>1</v>
@@ -1773,7 +1775,7 @@
       <c r="H17" s="34">
         <v>1</v>
       </c>
-      <c r="I17" s="39"/>
+      <c r="I17" s="40"/>
     </row>
     <row r="18" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="49"/>
@@ -1782,25 +1784,25 @@
       </c>
       <c r="D18" s="24">
         <f>IF(D$17=1, D$16*Assets!$K5, -D$8*Assets!$K5)</f>
-        <v>313.28539203747096</v>
+        <v>295.53414948571475</v>
       </c>
       <c r="E18" s="24">
         <f>IF(E$17=1, E$16*Assets!$K5, -E$8*Assets!$K5)</f>
-        <v>110.15519482265093</v>
+        <v>109.85524351401405</v>
       </c>
       <c r="F18" s="24">
         <f>IF(F$17=1, F$16*Assets!$K5, -F$8*Assets!$K5)</f>
-        <v>283.03734580989044</v>
+        <v>142.13025194029856</v>
       </c>
       <c r="G18" s="24">
         <f>IF(G$17=1, G$16*Assets!$K5, -G$8*Assets!$K5)</f>
-        <v>0</v>
+        <v>117.7860913931889</v>
       </c>
       <c r="H18" s="24">
         <f>IF(H$17=1, H$16*Assets!$K5, -H$8*Assets!$K5)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="39"/>
+      <c r="I18" s="40"/>
     </row>
     <row r="19" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="49"/>
@@ -1809,25 +1811,25 @@
       </c>
       <c r="D19" s="24">
         <f>IF(D$17=1, D$16*Assets!$K6, -D$8*Assets!$K6)</f>
-        <v>234.96404402810322</v>
+        <v>221.65061211428608</v>
       </c>
       <c r="E19" s="24">
         <f>IF(E$17=1, E$16*Assets!$K6, -E$8*Assets!$K6)</f>
-        <v>82.616396116988184</v>
+        <v>82.391432635510526</v>
       </c>
       <c r="F19" s="24">
         <f>IF(F$17=1, F$16*Assets!$K6, -F$8*Assets!$K6)</f>
-        <v>212.27800935741783</v>
+        <v>106.59768895522392</v>
       </c>
       <c r="G19" s="24">
         <f>IF(G$17=1, G$16*Assets!$K6, -G$8*Assets!$K6)</f>
-        <v>0</v>
+        <v>88.339568544891662</v>
       </c>
       <c r="H19" s="24">
         <f>IF(H$17=1, H$16*Assets!$K6, -H$8*Assets!$K6)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="39"/>
+      <c r="I19" s="40"/>
     </row>
     <row r="20" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="49"/>
@@ -1836,25 +1838,25 @@
       </c>
       <c r="D20" s="24">
         <f>IF(D$17=1, D$16*Assets!$K7, -D$8*Assets!$K7)</f>
-        <v>156.64269601873548</v>
+        <v>147.76707474285737</v>
       </c>
       <c r="E20" s="24">
         <f>IF(E$17=1, E$16*Assets!$K7, -E$8*Assets!$K7)</f>
-        <v>55.077597411325463</v>
+        <v>54.927621757007024</v>
       </c>
       <c r="F20" s="24">
         <f>IF(F$17=1, F$16*Assets!$K7, -F$8*Assets!$K7)</f>
-        <v>141.51867290494522</v>
+        <v>71.065125970149282</v>
       </c>
       <c r="G20" s="24">
         <f>IF(G$17=1, G$16*Assets!$K7, -G$8*Assets!$K7)</f>
-        <v>0</v>
+        <v>58.893045696594449</v>
       </c>
       <c r="H20" s="24">
         <f>IF(H$17=1, H$16*Assets!$K7, -H$8*Assets!$K7)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="39"/>
+      <c r="I20" s="40"/>
     </row>
     <row r="21" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="49"/>
@@ -1863,88 +1865,88 @@
       </c>
       <c r="D21" s="24">
         <f>IF(D$17=1, D$16*Assets!$K8, -D$8*Assets!$K8)</f>
-        <v>78.321348009367739</v>
+        <v>73.883537371428687</v>
       </c>
       <c r="E21" s="24">
         <f>IF(E$17=1, E$16*Assets!$K8, -E$8*Assets!$K8)</f>
-        <v>27.538798705662732</v>
+        <v>27.463810878503512</v>
       </c>
       <c r="F21" s="24">
         <f>IF(F$17=1, F$16*Assets!$K8, -F$8*Assets!$K8)</f>
-        <v>70.75933645247261</v>
+        <v>35.532562985074641</v>
       </c>
       <c r="G21" s="24">
         <f>IF(G$17=1, G$16*Assets!$K8, -G$8*Assets!$K8)</f>
-        <v>0</v>
+        <v>29.446522848297224</v>
       </c>
       <c r="H21" s="24">
         <f>IF(H$17=1, H$16*Assets!$K8, -H$8*Assets!$K8)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="39"/>
+      <c r="I21" s="40"/>
     </row>
     <row r="22" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="10"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B23" s="54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="31">
         <f>D8+D16</f>
-        <v>9380.2134800936765</v>
+        <v>9335.8353737142861</v>
       </c>
       <c r="E23" s="31">
         <f>E8+E16</f>
-        <v>1149.3879870566273</v>
+        <v>1148.638108785035</v>
       </c>
       <c r="F23" s="31">
         <f>F8+F16</f>
-        <v>707.5933645247261</v>
+        <v>592.3256298507464</v>
       </c>
       <c r="G23" s="31">
         <f>G8+G16</f>
-        <v>0</v>
+        <v>491.46522848297224</v>
       </c>
       <c r="H23" s="31">
         <f>H8+H16</f>
         <v>0</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B24" s="52"/>
       <c r="C24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="41">
+        <v>44</v>
+      </c>
+      <c r="D24" s="42">
         <f>IF(D10&gt;0,(((D8*D9)+(D16*D12))/(D8+D16)),0)</f>
-        <v>20379.432063639018</v>
-      </c>
-      <c r="E24" s="41">
+        <v>20404.378926426198</v>
+      </c>
+      <c r="E24" s="42">
         <f>IF(E10&gt;0,(((E8*E9)+(E16*E12))/(E8+E16)),0)</f>
-        <v>124738.18165365637</v>
-      </c>
-      <c r="F24" s="41">
+        <v>124381.16133123841</v>
+      </c>
+      <c r="F24" s="42">
         <f>IF(F10&gt;0,(((F8*F9)+(F16*F12))/(F8+F16)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="41">
+        <v>40200.000000000007</v>
+      </c>
+      <c r="G24" s="42">
         <f>IF(G10&gt;0,(((G8*G9)+(G16*G12))/(G8+G16)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="41">
+        <v>48450</v>
+      </c>
+      <c r="H24" s="42">
         <f>IF(H10&gt;0,(((H8*H9)+(H16*H12))/(H8+H16)),0)</f>
         <v>0</v>
       </c>
@@ -1957,35 +1959,35 @@
       </c>
       <c r="D25" s="24">
         <f>D23*D24</f>
-        <v>191163423.36000001</v>
+        <v>190491922.56000003</v>
       </c>
       <c r="E25" s="24">
         <f>E23*E24</f>
-        <v>143372567.52000001</v>
+        <v>142868941.92000002</v>
       </c>
       <c r="F25" s="24">
         <f>F23*F24</f>
-        <v>0</v>
+        <v>23811490.320000008</v>
       </c>
       <c r="G25" s="24">
         <f>G23*G24</f>
-        <v>0</v>
+        <v>23811490.320000004</v>
       </c>
       <c r="H25" s="24">
         <f>H23*H24</f>
         <v>0</v>
       </c>
-      <c r="I25" s="42">
+      <c r="I25" s="43">
         <f>SUM(D25:G25)</f>
-        <v>334535990.88</v>
+        <v>380983845.12</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B27" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="15">
         <v>46161</v>
@@ -1993,28 +1995,28 @@
       <c r="E27" s="15">
         <v>46148</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
       <c r="I27" s="19">
         <f>I28/I$10</f>
-        <v>9.8070163422183648E-3</v>
+        <v>9.1604621015079473E-3</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B28" s="53"/>
       <c r="C28" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="24">
         <v>2549100</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="24">
         <v>100905</v>
       </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
       <c r="I28" s="44">
         <f>SUM(D28:H28)</f>
         <v>2650005</v>
@@ -2023,19 +2025,19 @@
     <row r="30" spans="2:9" x14ac:dyDescent="0.45">
       <c r="D30" s="45">
         <f>D18*D12</f>
-        <v>8026371.7440000055</v>
+        <v>7757771.4240000118</v>
       </c>
       <c r="E30" s="45">
         <f>E18*E12</f>
-        <v>17701939.808000006</v>
+        <v>17500489.568000007</v>
       </c>
       <c r="F30" s="45">
         <f>F18*F12</f>
-        <v>9558171.1679999996</v>
+        <v>5713636.1280000024</v>
       </c>
       <c r="G30" s="45">
         <f>G18*G12</f>
-        <v>0</v>
+        <v>5706736.1280000024</v>
       </c>
       <c r="H30" s="45">
         <f>H18*H12</f>
@@ -2058,62 +2060,62 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D16:D17">
-    <cfRule type="expression" dxfId="32" priority="2">
+    <cfRule type="expression" dxfId="32" priority="16">
       <formula>#REF!+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D21">
-    <cfRule type="expression" dxfId="31" priority="10">
+    <cfRule type="expression" dxfId="31" priority="24">
       <formula>#REF!+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:E22">
-    <cfRule type="expression" dxfId="30" priority="11">
+  <conditionalFormatting sqref="D22:F22">
+    <cfRule type="expression" dxfId="30" priority="25">
       <formula>B22+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:I13">
-    <cfRule type="expression" dxfId="29" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="5" stopIfTrue="1">
       <formula>D13&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:I14">
-    <cfRule type="expression" dxfId="28" priority="7">
+    <cfRule type="expression" dxfId="28" priority="3">
       <formula>D13&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:I14">
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="27" priority="4">
       <formula>D14&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:I15">
-    <cfRule type="expression" dxfId="26" priority="4">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>#REF!+C15&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16:F17">
+  <conditionalFormatting sqref="E16:G17">
     <cfRule type="expression" dxfId="25" priority="1">
       <formula>C16+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E18:F21">
-    <cfRule type="expression" dxfId="24" priority="13">
+  <conditionalFormatting sqref="E18:G21">
+    <cfRule type="expression" dxfId="24" priority="6">
       <formula>#REF!+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="expression" dxfId="23" priority="92">
-      <formula>E22+#REF!&gt;0</formula>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="expression" dxfId="23" priority="7">
+      <formula>F22+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:H22">
-    <cfRule type="expression" dxfId="22" priority="3">
+  <conditionalFormatting sqref="H16:H22">
+    <cfRule type="expression" dxfId="22" priority="17">
       <formula>#REF!+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I22">
-    <cfRule type="expression" dxfId="21" priority="62">
+    <cfRule type="expression" dxfId="21" priority="76">
       <formula>G16+#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2124,24 +2126,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="22" customWidth="1"/>
     <col min="2" max="2" width="11" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" style="22" customWidth="1"/>
-    <col min="5" max="5" width="34.33203125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" style="22" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -2150,62 +2154,62 @@
         <v>2</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B3" s="52"/>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="52"/>
     </row>
     <row r="4" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="53"/>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" s="53"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="61">
-        <v>1</v>
-      </c>
-      <c r="E5" s="61">
+        <v>28</v>
+      </c>
+      <c r="D5" s="30">
+        <v>0.7</v>
+      </c>
+      <c r="E5" s="30">
         <v>0</v>
       </c>
       <c r="F5" s="18">
         <f>SUM(A5:E5)</f>
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="52"/>
       <c r="C6" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="61">
+        <v>29</v>
+      </c>
+      <c r="D6" s="30">
         <v>1</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="30">
         <v>0</v>
       </c>
       <c r="F6" s="18"/>
@@ -2213,11 +2217,11 @@
     <row r="7" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="53"/>
       <c r="C7" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="31">
         <f>Assets!$E$6*(D5)*D6</f>
-        <v>123930727</v>
+        <v>88219426.399999991</v>
       </c>
       <c r="E7" s="31">
         <f>Assets!$E$6*(E5)*E6</f>
@@ -2225,18 +2229,18 @@
       </c>
       <c r="F7" s="35">
         <f>SUM(D7:E7)</f>
-        <v>123930727</v>
+        <v>88219426.399999991</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="59">
-        <v>10063</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="34">
+        <v>8876</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="8"/>
@@ -2244,10 +2248,10 @@
     <row r="9" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="52"/>
       <c r="C9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="59">
-        <v>9792</v>
+        <v>33</v>
+      </c>
+      <c r="D9" s="34">
+        <v>9883</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="8"/>
@@ -2259,7 +2263,7 @@
       </c>
       <c r="D10" s="31">
         <f>D9*D8</f>
-        <v>98536896</v>
+        <v>87721508</v>
       </c>
       <c r="E10" s="31">
         <f>E9*E8</f>
@@ -2267,13 +2271,13 @@
       </c>
       <c r="F10" s="35">
         <f>SUM(D10:E10)</f>
-        <v>98536896</v>
+        <v>87721508</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="53"/>
       <c r="C11" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="36">
         <f>IFERROR(D10/$F$10, 0)</f>
@@ -2290,27 +2294,27 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="38">
-        <v>10770</v>
+        <v>10940</v>
       </c>
       <c r="E12" s="38">
-        <v>46330</v>
+        <v>49355</v>
       </c>
       <c r="F12" s="23"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="58"/>
       <c r="C13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="9">
         <f>IF(D9&gt;0, (D12-D9)/D9, 0)</f>
-        <v>9.9877450980392163E-2</v>
+        <v>0.1069513305676414</v>
       </c>
       <c r="E13" s="9">
         <f>IF(E9&gt;0, (E12-E9)/E9, 0)</f>
@@ -2318,35 +2322,35 @@
       </c>
       <c r="F13" s="9">
         <f>IFERROR(F14/F10, 0)</f>
-        <v>9.9877450980392163E-2</v>
+        <v>0.1069513305676414</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="58"/>
       <c r="C14" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="39">
+        <v>38</v>
+      </c>
+      <c r="D14" s="40">
         <f>D10*D13</f>
-        <v>9841614</v>
-      </c>
-      <c r="E14" s="39">
+        <v>9381932</v>
+      </c>
+      <c r="E14" s="40">
         <f>E10*E13</f>
         <v>0</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="40">
         <f>SUM(D14:E14)</f>
-        <v>9841614</v>
+        <v>9381932</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="58"/>
       <c r="C15" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="24">
         <f>D7-D10</f>
-        <v>25393831</v>
+        <v>497918.39999999106</v>
       </c>
       <c r="E15" s="24">
         <f>E7-E10</f>
@@ -2354,31 +2358,31 @@
       </c>
       <c r="F15" s="24">
         <f>SUM(A15:D15)</f>
-        <v>25393831</v>
+        <v>497918.39999999106</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="58"/>
       <c r="C16" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="39">
+        <v>39</v>
+      </c>
+      <c r="D16" s="40">
         <f>IFERROR((D7-D10)/D12, 0)</f>
-        <v>2357.8301764159701</v>
-      </c>
-      <c r="E16" s="39">
+        <v>45.513564899450735</v>
+      </c>
+      <c r="E16" s="40">
         <f>IFERROR((E7-E10)/E12, 0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>IFERROR((F7-F10)/F12, 0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="58"/>
       <c r="C17" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="34">
         <v>1</v>
@@ -2386,132 +2390,132 @@
       <c r="E17" s="34">
         <v>1</v>
       </c>
-      <c r="F17" s="39"/>
-    </row>
-    <row r="18" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F17" s="40"/>
+    </row>
+    <row r="18" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="58"/>
       <c r="C18" s="14">
         <v>0.4</v>
       </c>
       <c r="D18" s="24">
         <f>IF(D$17=1, D$16*Assets!$K5, -D$8*Assets!$K5)</f>
-        <v>943.13207056638805</v>
+        <v>18.205425959780296</v>
       </c>
       <c r="E18" s="24">
         <f>IF(E$17=1, E$16*Assets!$K5, -E$8*Assets!$K5)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="39"/>
-    </row>
-    <row r="19" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F18" s="40"/>
+    </row>
+    <row r="19" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="58"/>
       <c r="C19" s="14">
         <v>0.3</v>
       </c>
       <c r="D19" s="24">
         <f>IF(D$17=1, D$16*Assets!$K6, -D$8*Assets!$K6)</f>
-        <v>707.34905292479095</v>
+        <v>13.654069469835219</v>
       </c>
       <c r="E19" s="24">
         <f>IF(E$17=1, E$16*Assets!$K6, -E$8*Assets!$K6)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="39"/>
-    </row>
-    <row r="20" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F19" s="40"/>
+    </row>
+    <row r="20" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="58"/>
       <c r="C20" s="14">
         <v>0.2</v>
       </c>
       <c r="D20" s="24">
         <f>IF(D$17=1, D$16*Assets!$K7, -D$8*Assets!$K7)</f>
-        <v>471.56603528319403</v>
+        <v>9.102712979890148</v>
       </c>
       <c r="E20" s="24">
         <f>IF(E$17=1, E$16*Assets!$K7, -E$8*Assets!$K7)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="39"/>
-    </row>
-    <row r="21" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" s="40"/>
+    </row>
+    <row r="21" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="58"/>
       <c r="C21" s="14">
         <v>0.1</v>
       </c>
       <c r="D21" s="24">
         <f>IF(D$17=1, D$16*Assets!$K8, -D$8*Assets!$K8)</f>
-        <v>235.78301764159701</v>
+        <v>4.551356489945074</v>
       </c>
       <c r="E21" s="24">
         <f>IF(E$17=1, E$16*Assets!$K8, -E$8*Assets!$K8)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="39"/>
-    </row>
-    <row r="22" spans="2:6" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F21" s="40"/>
+    </row>
+    <row r="22" spans="2:9" s="21" customFormat="1" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="10"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B23" s="54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="31">
         <f>D8+D16</f>
-        <v>12420.83017641597</v>
+        <v>8921.513564899451</v>
       </c>
       <c r="E23" s="31">
         <f>E8+E16</f>
         <v>0</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B24" s="52"/>
       <c r="C24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="41">
+        <v>44</v>
+      </c>
+      <c r="D24" s="42">
         <f>IF(D10&gt;0,(((D8*D9)+(D16*D12))/(D8+D16)),0)</f>
-        <v>9977.652478923128</v>
-      </c>
-      <c r="E24" s="41">
+        <v>9888.3923404082452</v>
+      </c>
+      <c r="E24" s="42">
         <f>IF(E10&gt;0,(((E8*E9)+(E16*E12))/(E8+E16)),0)</f>
         <v>0</v>
       </c>
       <c r="F24" s="53"/>
     </row>
-    <row r="25" spans="2:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="53"/>
       <c r="C25" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="46">
         <f>D23*D24</f>
-        <v>123930727</v>
+        <v>88219426.399999991</v>
       </c>
       <c r="E25" s="46">
         <f>E23*E24</f>
         <v>0</v>
       </c>
-      <c r="F25" s="42">
+      <c r="F25" s="43">
         <f>SUM(D25:E25)</f>
-        <v>123930727</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
+        <v>88219426.399999991</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B27" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="15">
         <v>46148</v>
@@ -2521,13 +2525,17 @@
       </c>
       <c r="F27" s="19">
         <f>F28/F$10</f>
-        <v>1.4972107503771988E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
+        <v>1.6818053333054875E-2</v>
+      </c>
+      <c r="H27" s="59">
+        <f>F27*12</f>
+        <v>0.2018166399966585</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B28" s="53"/>
       <c r="C28" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="24">
         <v>1434641</v>
@@ -2539,11 +2547,17 @@
         <f>SUM(D28:E28)</f>
         <v>1475305</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="D30" s="62">
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="D30" s="45">
         <f>D18*D12</f>
-        <v>10157532.399999999</v>
+        <v>199167.35999999644</v>
       </c>
     </row>
   </sheetData>
@@ -2551,10 +2565,10 @@
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B8:B11"/>
-    <mergeCell ref="F23:F24"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="B12:B21"/>
     <mergeCell ref="B2:B4"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="B5:B7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2618,10 +2632,10 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B2" s="55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -2630,16 +2644,16 @@
         <v>2</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B3" s="52"/>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="52"/>
@@ -2647,20 +2661,20 @@
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B4" s="53"/>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="53"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="30">
         <v>1</v>
@@ -2674,7 +2688,7 @@
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="52"/>
       <c r="C6" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="30">
         <v>1</v>
@@ -2685,11 +2699,11 @@
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="53"/>
       <c r="C7" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" s="31">
         <f>Assets!$E$7*(D5)*D6</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
       <c r="E7" s="31">
         <f>Assets!$E$5*(E5)*E6</f>
@@ -2697,15 +2711,15 @@
       </c>
       <c r="F7" s="35">
         <f>SUM(A7:D7)</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="34">
         <v>1771</v>
@@ -2716,7 +2730,7 @@
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="52"/>
       <c r="C9" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="34">
         <v>7687</v>
@@ -2745,7 +2759,7 @@
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="53"/>
       <c r="C11" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="36">
         <f>IFERROR(D10/$F$10, 0)</f>
@@ -2762,13 +2776,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="60">
-        <v>7745</v>
+        <v>36</v>
+      </c>
+      <c r="D12" s="38">
+        <v>7805</v>
       </c>
       <c r="E12" s="47"/>
       <c r="F12" s="23"/>
@@ -2776,11 +2790,11 @@
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="58"/>
       <c r="C13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="9">
         <f>IF(D9&gt;0, (D12-D9)/D9, 0)</f>
-        <v>7.5452061922726679E-3</v>
+        <v>1.5350591908416807E-2</v>
       </c>
       <c r="E13" s="9">
         <f>IF(E9&gt;0, (E12-E9)/E9, 0)</f>
@@ -2788,35 +2802,35 @@
       </c>
       <c r="F13" s="9">
         <f>IFERROR(F14/F10, 0)</f>
-        <v>7.5452061922726679E-3</v>
+        <v>1.5350591908416807E-2</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="58"/>
       <c r="C14" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="39">
+        <v>38</v>
+      </c>
+      <c r="D14" s="40">
         <f>D10*D13</f>
-        <v>102718</v>
-      </c>
-      <c r="E14" s="39">
+        <v>208978</v>
+      </c>
+      <c r="E14" s="40">
         <f>E10*E13</f>
         <v>0</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="40">
         <f>SUM(A14:D14)</f>
-        <v>102718</v>
+        <v>208978</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="58"/>
       <c r="C15" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="24">
         <f>D7-D10</f>
-        <v>40113</v>
+        <v>8855</v>
       </c>
       <c r="E15" s="24">
         <f>E7-E10</f>
@@ -2824,23 +2838,23 @@
       </c>
       <c r="F15" s="24">
         <f>SUM(A15:D15)</f>
-        <v>40113</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="58"/>
       <c r="C16" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="39">
+        <v>39</v>
+      </c>
+      <c r="D16" s="40">
         <f>IFERROR((D7-D10)/D12, 0)</f>
-        <v>5.1792123950936091</v>
-      </c>
-      <c r="E16" s="39">
+        <v>1.1345291479820627</v>
+      </c>
+      <c r="E16" s="40">
         <f>IFERROR((E7-E10)/E12, 0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="40">
         <f>IFERROR((F7-F10)/F12, 0)</f>
         <v>0</v>
       </c>
@@ -2848,7 +2862,7 @@
     <row r="17" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="58"/>
       <c r="C17" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="34">
         <v>1</v>
@@ -2856,7 +2870,7 @@
       <c r="E17" s="34">
         <v>1</v>
       </c>
-      <c r="F17" s="39"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="58"/>
@@ -2865,13 +2879,13 @@
       </c>
       <c r="D18" s="24">
         <f>IF(D$17=1, D$16*Assets!$K5, -D$8*Assets!$K5)</f>
-        <v>2.0716849580374439</v>
+        <v>0.45381165919282512</v>
       </c>
       <c r="E18" s="24">
         <f>IF(E$17=1, E$16*Assets!$K5, -E$8*Assets!$K5)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="39"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="58"/>
@@ -2880,13 +2894,13 @@
       </c>
       <c r="D19" s="24">
         <f>IF(D$17=1, D$16*Assets!$K6, -D$8*Assets!$K6)</f>
-        <v>1.5537637185280826</v>
+        <v>0.34035874439461883</v>
       </c>
       <c r="E19" s="24">
         <f>IF(E$17=1, E$16*Assets!$K6, -E$8*Assets!$K6)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="39"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="20" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="58"/>
@@ -2895,13 +2909,13 @@
       </c>
       <c r="D20" s="24">
         <f>IF(D$17=1, D$16*Assets!$K7, -D$8*Assets!$K7)</f>
-        <v>1.035842479018722</v>
+        <v>0.22690582959641256</v>
       </c>
       <c r="E20" s="24">
         <f>IF(E$17=1, E$16*Assets!$K7, -E$8*Assets!$K7)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="39"/>
+      <c r="F20" s="40"/>
     </row>
     <row r="21" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="58"/>
@@ -2910,49 +2924,49 @@
       </c>
       <c r="D21" s="24">
         <f>IF(D$17=1, D$16*Assets!$K8, -D$8*Assets!$K8)</f>
-        <v>0.51792123950936098</v>
+        <v>0.11345291479820628</v>
       </c>
       <c r="E21" s="24">
         <f>IF(E$17=1, E$16*Assets!$K8, -E$8*Assets!$K8)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="39"/>
+      <c r="F21" s="40"/>
     </row>
     <row r="22" spans="2:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C22" s="10"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="31">
         <f>D8+D16</f>
-        <v>1776.1792123950936</v>
+        <v>1772.134529147982</v>
       </c>
       <c r="E23" s="31">
         <f>E8+E16</f>
         <v>0</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="52"/>
       <c r="C24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="41">
+        <v>44</v>
+      </c>
+      <c r="D24" s="42">
         <f>IF(D10&gt;0,(((D8*D9)+(D16*D12))/(D8+D16)),0)</f>
-        <v>7687.1691238794028</v>
-      </c>
-      <c r="E24" s="41">
+        <v>7687.0755441741358</v>
+      </c>
+      <c r="E24" s="42">
         <f>IF(E10&gt;0,(((E8*E9)+(E16*E12))/(E8+E16)),0)</f>
         <v>0</v>
       </c>
@@ -2961,27 +2975,27 @@
     <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="53"/>
       <c r="C25" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="46">
         <f>D23*D24</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
       <c r="E25" s="46">
         <f>E23*E24</f>
         <v>0</v>
       </c>
-      <c r="F25" s="42">
+      <c r="F25" s="43">
         <f>SUM(A25:D25)</f>
-        <v>13653790</v>
+        <v>13622532</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="15">
         <v>46161</v>
@@ -2995,7 +3009,7 @@
     <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="53"/>
       <c r="C28" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="24">
         <v>136591</v>
@@ -3010,12 +3024,12 @@
   <mergeCells count="8">
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="B12:B21"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D17:D21">
